--- a/test/customer-journey/CosmoEdge-客户旅程测试用例.xlsx
+++ b/test/customer-journey/CosmoEdge-客户旅程测试用例.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R395eb8ff81794827"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户旅程" sheetId="2" r:id="R787b3ed7a0f04258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细用例" sheetId="3" r:id="R73dc64fc59d04ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备矩阵" sheetId="4" r:id="Rb6b78430c6754559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源与缺口" sheetId="5" r:id="R7bd6f8a90c43475b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能覆盖" sheetId="6" r:id="R499d909fe4de430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算法覆盖" sheetId="7" r:id="Re4cf4ac8c04b4019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件覆盖" sheetId="8" r:id="R5720b84b78c34a9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数覆盖" sheetId="9" r:id="R1b70e2af9c8549ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口覆盖" sheetId="10" r:id="Rd61f10641cac4a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充检查" sheetId="11" r:id="R5aeae46e6f0e409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="Reb80d4cc579641e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户旅程" sheetId="2" r:id="R45ea7e73c0684748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细用例" sheetId="3" r:id="R96ee922028ea4219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备矩阵" sheetId="4" r:id="Rbd69ea9a343c4395"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源与缺口" sheetId="5" r:id="R38f691ad12284363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能覆盖" sheetId="6" r:id="R8a6446da02994f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算法覆盖" sheetId="7" r:id="R4c90900f26dc42f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件覆盖" sheetId="8" r:id="R037a9d8a1d9f4374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数覆盖" sheetId="9" r:id="R849b99609d114bec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口覆盖" sheetId="10" r:id="R40f361b611ef46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充检查" sheetId="11" r:id="R1065fad83c224c13"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -188,6 +188,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -373,8 +376,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TestCases" displayName="TestCases" ref="A4:AC331" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:AC331"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TestCases" displayName="TestCases" ref="A4:AC335" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:AC335"/>
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="用例ID"/>
     <x:tableColumn id="2" name="旅程"/>
@@ -429,8 +432,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Resources" displayName="Resources" ref="A4:G37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:G37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Resources" displayName="Resources" ref="A4:G39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:G39"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="资源编号"/>
     <x:tableColumn id="2" name="资源名称"/>
@@ -759,7 +762,7 @@
         <x:v>用例总数</x:v>
       </x:c>
       <x:c r="B5" s="10" t="n">
-        <x:v>327</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -767,7 +770,7 @@
         <x:v>已通过</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P329,"通过")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P335,"通过")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -776,7 +779,7 @@
         <x:v>失败</x:v>
       </x:c>
       <x:c r="B7" s="10" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P329,"失败")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P335,"失败")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -785,7 +788,7 @@
         <x:v>阻塞</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P329,"阻塞")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P335,"阻塞")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -794,7 +797,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:v>327</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -802,7 +805,7 @@
         <x:v>部分完成</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P329,"部分完成")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P335,"部分完成")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -811,7 +814,7 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P329,"不适用")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P335,"不适用")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -860,7 +863,7 @@
         <x:v>文档性质</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>由v0.1评审稿持续维护的可执行主库；327条用例，不代表已经实测通过。</x:v>
+        <x:v>由v0.1评审稿持续维护的可执行主库；331条用例，不代表已经实测通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
@@ -988,7 +991,7 @@
         <x:v>用例库版本</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>1.4.0</x:v>
+        <x:v>1.6.0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
@@ -6591,7 +6594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re792138b61254039"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfae229dff67a4545"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6636,7 +6639,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27add4b6476d4567"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08446b71f5a54c84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6857,7 +6860,7 @@
         <x:v>实时画面、落库记录和统计形成一致证据</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>LIVE → EVENT</x:v>
+        <x:v>LIVE → EVENT（含EVENT-012/013/014事件上报审核）</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
         <x:v>开多窗及叠加 → 触发告警 → 看详情与录像 → 按条件筛选 → 查人脸车辆流量 → 导出对账 → 关闭播放器</x:v>
@@ -6961,7 +6964,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bec410091484d7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ff68db9cc054274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8680,7 +8683,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；逐台执行 CAM-HK-A、CAM-DH、CAM-HK-B、CAM-UNV</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
         <x:v>1. 点击新增选择RTSP
@@ -8716,7 +8719,7 @@
       <x:c r="R27" s="12" t="str"/>
       <x:c r="S27" s="12" t="str"/>
       <x:c r="T27" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U27" s="4" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -8752,7 +8755,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；已核对 NVR 逻辑通道与实际画面</x:v>
       </x:c>
       <x:c r="G28" s="17" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H28" s="17" t="str">
         <x:v>1. 逐路新增 NVR 的4个视频源
@@ -8788,7 +8791,7 @@
       <x:c r="R28" s="17" t="str"/>
       <x:c r="S28" s="17" t="str"/>
       <x:c r="T28" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U28" s="17" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A；ONVIF-SETTINGS</x:v>
@@ -8824,7 +8827,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；FACE-VIDEO</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
         <x:v>1. 新增本地视频
@@ -8860,7 +8863,7 @@
       <x:c r="R29" s="12" t="str"/>
       <x:c r="S29" s="12" t="str"/>
       <x:c r="T29" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U29" s="4" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A；FACE-VIDEO</x:v>
@@ -8896,7 +8899,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；短视频更适合次数核对</x:v>
       </x:c>
       <x:c r="G30" s="17" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H30" s="17" t="str">
         <x:v>1. 依次设0、1、2次
@@ -8931,7 +8934,7 @@
       <x:c r="R30" s="17" t="str"/>
       <x:c r="S30" s="17" t="str"/>
       <x:c r="T30" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U30" s="17" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A；FACE-VIDEO</x:v>
@@ -8967,7 +8970,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
         <x:v>1. 编辑名称和合法地址
@@ -9003,7 +9006,7 @@
       <x:c r="R31" s="12" t="str"/>
       <x:c r="S31" s="12" t="str"/>
       <x:c r="T31" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U31" s="4" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -9039,7 +9042,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；错误值只用于本轮通道</x:v>
       </x:c>
       <x:c r="G32" s="17" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H32" s="17" t="str">
         <x:v>1. 输入空地址、不支持协议、不可达端口和错误凭据
@@ -9074,7 +9077,7 @@
       <x:c r="R32" s="17" t="str"/>
       <x:c r="S32" s="17" t="str"/>
       <x:c r="T32" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U32" s="17" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -9110,7 +9113,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；各厂商实际支持的 H264/H265/主子码流；更改摄像机配置需执行授权</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
         <x:v>1. 以相同业务分别接入实际码流
@@ -9145,7 +9148,7 @@
       <x:c r="R33" s="12" t="str"/>
       <x:c r="S33" s="12" t="str"/>
       <x:c r="T33" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U33" s="4" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -9181,7 +9184,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；隔离源或获准断流窗口</x:v>
       </x:c>
       <x:c r="G34" s="17" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H34" s="17" t="str">
         <x:v>1. 运行任务并预览
@@ -9217,7 +9220,7 @@
       <x:c r="R34" s="17" t="str"/>
       <x:c r="S34" s="17" t="str"/>
       <x:c r="T34" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U34" s="17" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -9253,7 +9256,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；本轮有无任务通道各一个</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
         <x:v>1. 取消一次删除
@@ -9289,7 +9292,7 @@
       <x:c r="R35" s="12" t="str"/>
       <x:c r="S35" s="12" t="str"/>
       <x:c r="T35" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U35" s="4" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -9305,7 +9308,7 @@
       <x:c r="AB35" s="4" t="str"/>
       <x:c r="AC35" s="4" t="str"/>
     </x:row>
-    <x:row r="36" ht="68" customHeight="1">
+    <x:row r="36" ht="217.5" customHeight="1">
       <x:c r="A36" s="17" t="str">
         <x:v>CAM-010</x:v>
       </x:c>
@@ -9316,31 +9319,32 @@
         <x:v>视频源基础接入</x:v>
       </x:c>
       <x:c r="D36" s="17" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="E36" s="17" t="str">
-        <x:v>USB 摄像头</x:v>
+        <x:v>USB 摄像头发现、预览与算法运行（必测）</x:v>
       </x:c>
       <x:c r="F36" s="17" t="str">
-        <x:v>已登录；合法取流地址由设备读取或用户确认；USB设备待补且目标支持</x:v>
+        <x:v>USB 摄像头已纳入必测，开测核对现有硬件枚举和当前画面；已登录且基础检测场景可运行。不得沿用历史缺资源结论跳过。</x:v>
       </x:c>
       <x:c r="G36" s="17" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>DUT；USB-CAMERA；MODEL-INVENTORY</x:v>
       </x:c>
       <x:c r="H36" s="17" t="str">
-        <x:v>1. 打开USB列表
-2. 选择设备新增
-3. 预览抓拍
-4. 受控拔插再恢复</x:v>
+        <x:v>1. 刷新USB列表，核对设备标识与现场硬件
+2. 选择设备新增本轮通道，预览并抓拍，确认当前画面
+3. 绑定基础检测场景，启动后让目标进入画面并观察30–60秒，核对真实检测结果
+4. 停止后确认无新增结果，再启动并核对新时间戳结果
+5. 具备现场操作条件时受控拔插并恢复；清理本轮对象，保留原有任务</x:v>
       </x:c>
       <x:c r="I36" s="17" t="str">
-        <x:v>列表与实际硬件一致；异常可解释；恢复后无重复通道；缺硬件记阻塞。</x:v>
+        <x:v>USB发现、预览、抓拍、算法输出、启停恢复均需实测。设备标识一致且无重复通道；未识别时记录当次证据并排查，不直接按历史资源不足跳过。拔插条件不具备只影响拔插子步骤。</x:v>
       </x:c>
       <x:c r="J36" s="17" t="str">
-        <x:v>停止本轮任务后删除本轮通道；恢复视频重复次数</x:v>
+        <x:v>停止并删除本轮创建的任务和通道；恢复原USB连接及配置；不得停止或删除用户原有任务。</x:v>
       </x:c>
       <x:c r="K36" s="17" t="str">
-        <x:v>步骤观察、实际结果、证据文件与清理核对</x:v>
+        <x:v>USB设备标识、当前预览/抓拍、真实目标输出、任务ID与启停时间、拔插条件及恢复清理记录。</x:v>
       </x:c>
       <x:c r="L36" s="17" t="str">
         <x:v>UI主操作＋API只读核对</x:v>
@@ -9349,7 +9353,7 @@
         <x:v>受影响模块回归</x:v>
       </x:c>
       <x:c r="N36" s="17" t="str">
-        <x:v>目标设备具备该能力</x:v>
+        <x:v>具备USB输入的目标必须执行；仅真实不支持该能力的其他平台可凭证据判不适用。</x:v>
       </x:c>
       <x:c r="O36" s="17" t="str">
         <x:v>src/web/src/views/gam/taskManager/index.vue；src/web/src/api/gam.js；docs/guide/test-cases.md</x:v>
@@ -9361,10 +9365,10 @@
       <x:c r="R36" s="17" t="str"/>
       <x:c r="S36" s="17" t="str"/>
       <x:c r="T36" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U36" s="17" t="str">
-        <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A；USB-CAMERA</x:v>
+        <x:v>DUT；USB-CAMERA；MODEL-INVENTORY</x:v>
       </x:c>
       <x:c r="V36" s="17" t="str">
         <x:v>codex-ui-and-evidence</x:v>
@@ -9397,7 +9401,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认；损坏MP4、无视频轨、空文件与后缀伪装的隔离副本</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
         <x:v>1. 逐个上传并创建通道
@@ -9432,7 +9436,7 @@
       <x:c r="R37" s="12" t="str"/>
       <x:c r="S37" s="12" t="str"/>
       <x:c r="T37" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U37" s="4" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A；FACE-VIDEO</x:v>
@@ -9468,7 +9472,7 @@
         <x:v>已登录；合法取流地址由设备读取或用户确认</x:v>
       </x:c>
       <x:c r="G38" s="17" t="str">
-        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB待补</x:v>
+        <x:v>四台摄像机；NVR-A；FACE-VIDEO；USB-CAMERA（接入用例必测，开测核对）</x:v>
       </x:c>
       <x:c r="H38" s="17" t="str">
         <x:v>1. 重复点击新增
@@ -9503,7 +9507,7 @@
       <x:c r="R38" s="17" t="str"/>
       <x:c r="S38" s="17" t="str"/>
       <x:c r="T38" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U38" s="17" t="str">
         <x:v>DUT；CAM-HK-A；CAM-DH；CAM-HK-B；CAM-UNV；NVR-A</x:v>
@@ -30584,6 +30588,309 @@
       <x:c r="AA331" s="34"/>
       <x:c r="AB331" s="34"/>
       <x:c r="AC331" s="34"/>
+    </x:row>
+    <x:row r="332" ht="210" customHeight="1">
+      <x:c r="A332" s="34" t="str">
+        <x:v>PERF-011</x:v>
+      </x:c>
+      <x:c r="B332" s="34" t="str">
+        <x:v>J12</x:v>
+      </x:c>
+      <x:c r="C332" s="34" t="str">
+        <x:v>容量稳定性与异常恢复</x:v>
+      </x:c>
+      <x:c r="D332" s="34" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E332" s="34" t="str">
+        <x:v>受保护 VLM 加载的主机内存接纳与恢复</x:v>
+      </x:c>
+      <x:c r="F332" s="34" t="str">
+        <x:v>专用 Sophon 测试设备、兼容的受保护本地 VLM、已知正负图片和可用视频源；有读取内核/进程及有界故障注入授权；记录原任务，不停止原任务腾出资源。</x:v>
+      </x:c>
+      <x:c r="G332" s="34" t="str">
+        <x:v>设备、模型、样本与故障注入范围由本轮私有配置绑定。</x:v>
+      </x:c>
+      <x:c r="H332" s="34" t="str">
+        <x:v>1. 记录主进程 PID、内核 OOM 计数、MemAvailable、模型大小和原任务输出；确认无同模型共享实例
+2. 在安全下限内启动有内存上限、自动退出的临时占用进程，使可用内存不足以加载该模型；无法安全形成条件时记录具体阻塞
+3. 通过页面创建临时 VLM 视频任务，核对初始化失败、日志和原任务持续输出；禁止以启用开关代替推理成功
+4. 释放本轮占用，确认内存达到加载条件后重试；完成正负图片问答及视频实际推理，不重启主进程掩盖恢复失败
+5. 停止并删除本轮任务，核对原配置、原任务、临时进程和新增 OOM 记录</x:v>
+      </x:c>
+      <x:c r="I332" s="34" t="str">
+        <x:v>内存不足时拒绝加载且无主进程 SIGKILL/重启，原任务继续工作；满足加载条件后实际推理成功；任务运行状态不得把初始化失败显示为正常推理。</x:v>
+      </x:c>
+      <x:c r="J332" s="34" t="str">
+        <x:v>结束本轮内存占用并验证退出；清理本轮图片/视频任务，恢复原配置；不得删除真实事件或关闭原任务。</x:v>
+      </x:c>
+      <x:c r="K332" s="34" t="str">
+        <x:v>首次失败与重试分别保留；记录内存、模型大小、进程 PID、内核 OOM、初始化日志、UI 状态、实际正负结果及恢复核对。</x:v>
+      </x:c>
+      <x:c r="L332" s="34" t="str">
+        <x:v>UI主操作＋有界压力脚本＋内核与接口交叉验证</x:v>
+      </x:c>
+      <x:c r="M332" s="34" t="str">
+        <x:v>受影响模块回归</x:v>
+      </x:c>
+      <x:c r="N332" s="34" t="str">
+        <x:v>Sophon 受保护本地 VLM；不以 x86 或小模型通过代替该设备大模型验收。</x:v>
+      </x:c>
+      <x:c r="O332" s="34" t="str">
+        <x:v>src/nn/guard/CemV2SophonLoader.cc；src/nn/device/sophon/qwen3vl/qwen3vl_runner.cc；实测 OOM 缺陷回归</x:v>
+      </x:c>
+      <x:c r="P332" s="34" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="Q332" s="32" t="str">
+        <x:v>新增回归编号；历史实测不自动转为此新用例通过。</x:v>
+      </x:c>
+      <x:c r="R332" s="34" t="str"/>
+      <x:c r="S332" s="34" t="str"/>
+      <x:c r="T332" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U332" s="4" t="str">
+        <x:v>DUT；MODEL-PACKAGES；SCENARIO-TRUTH；RECOVERY-KIT</x:v>
+      </x:c>
+      <x:c r="V332" s="4" t="str">
+        <x:v>codex-ui-and-evidence</x:v>
+      </x:c>
+      <x:c r="W332" s="4" t="str"/>
+      <x:c r="X332" s="4" t="str"/>
+      <x:c r="Y332" s="4" t="str"/>
+      <x:c r="Z332" s="4" t="str"/>
+      <x:c r="AA332" s="4" t="str"/>
+      <x:c r="AB332" s="4" t="str"/>
+      <x:c r="AC332" s="4" t="str"/>
+    </x:row>
+    <x:row r="333" ht="285" customHeight="1">
+      <x:c r="A333" s="34" t="str">
+        <x:v>EVENT-012</x:v>
+      </x:c>
+      <x:c r="B333" s="34" t="str">
+        <x:v>J08</x:v>
+      </x:c>
+      <x:c r="C333" s="34" t="str">
+        <x:v>事件中心与统计</x:v>
+      </x:c>
+      <x:c r="D333" s="34" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E333" s="34" t="str">
+        <x:v>事件上报大模型审核：本地模型放行与过滤</x:v>
+      </x:c>
+      <x:c r="F333" s="34" t="str">
+        <x:v>使用私有 FACE-VIDEO 绑定的视频。逐帧确认匹配与不匹配的人物目标，记录时间段、帧号/时间戳、目标框及人工判断。提示词如“穿红色衣服的人”；没有红衣正例时改用画面实际可辨认的衣着特征，不虚构正例。 复制基础行人检测/区域入侵场景到本轮隔离对象，上游使用普通检测节点，事件上报使用 BA_00004 的触发类事件；不得用独立 VLM 节点提前完成审核。固定ROI、告警间隔、去重、播放次数和时间窗。 本地VLM可选且可加载，HTTP测试接收端已就绪。</x:v>
+      </x:c>
+      <x:c r="G333" s="34" t="str">
+        <x:v>视频、审核模型与接口认证按资源ID绑定本轮私有配置。</x:v>
+      </x:c>
+      <x:c r="H333" s="34" t="str">
+        <x:v>1. 核对视频哈希和人工标注；至少选择一个提示词匹配目标ROI和一个不匹配目标ROI。同帧多人时分别标记，避免用画面中其他人的特征判当前目标。
+2. 关闭事件上报组件的大模型审核，重播固定片段，确认正负目标都实际到达上报节点并产生基线事件；保存目标ID、时间、抓拍和接收记录。
+3. 在事件上报组件开启审核，选择本地审核模型并填写已标注的衣着提示词，保存后刷新回读开关、模式、模型和提示词。
+4. 从相同起点重播正例片段，核对当前目标裁剪图的审核结果为“是”，相应事件落库并由HTTP接收；事件/目标/帧归属一致。
+5. 重播负例片段，核对同一候选目标确实触发审核且回答“否”，有审核过滤证据，普通告警列表与HTTP接收均无该候选事件；排除去重、时间计划和无检测导致的假过滤。
+6. 关闭审核再重播负例，确认事件恢复上报；核对原业务并清理本轮对象。</x:v>
+      </x:c>
+      <x:c r="I333" s="34" t="str">
+        <x:v>开关和本地模型保存回读一致；同一目标“是”放行、“否”过滤，关闭审核恢复基线上报。多人与多帧不得串用结果；每种结果均有候选输入、审核结果和事件/HTTP证据。</x:v>
+      </x:c>
+      <x:c r="J333" s="34" t="str">
+        <x:v>停止并删除本轮视频任务、临时通道与复制场景；恢复原推送、审核参数和视频播放配置。保留原有业务及历史事件，不修改共享模型服务。</x:v>
+      </x:c>
+      <x:c r="K333" s="34" t="str">
+        <x:v>视频哈希、标注片段与目标ROI、场景/任务/组件ID、审核模式、提示词与模型版本、审核调用及是/否结果、过滤记录、事件ID/抓拍/HTTP接收对账、修改前后配置与清理核对；认证信息脱敏。</x:v>
+      </x:c>
+      <x:c r="L333" s="34" t="str">
+        <x:v>UI主操作＋日志/接口只读交叉验证</x:v>
+      </x:c>
+      <x:c r="M333" s="34" t="str">
+        <x:v>受影响模块回归</x:v>
+      </x:c>
+      <x:c r="N333" s="34" t="str">
+        <x:v>本地Qwen类审核；仅触发类候选事件。使用实际目标裁剪图人工判断，不宣称整体识别精度。</x:v>
+      </x:c>
+      <x:c r="O333" s="34" t="str">
+        <x:v>src/flow/alarm/TaskAlarmLlmReview.cc；src/flow/alarm/TaskAlarmEventBuilder.cc；data/resource/aiboxresource_bm1688/layout/actions.json</x:v>
+      </x:c>
+      <x:c r="P333" s="34" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="Q333" s="32" t="str">
+        <x:v>按逐目标可见事实核对功能；不以一次问答或总告警数减少替代审核链路验收。</x:v>
+      </x:c>
+      <x:c r="R333" s="34"/>
+      <x:c r="S333" s="34"/>
+      <x:c r="T333" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U333" s="4" t="str">
+        <x:v>DUT；FACE-VIDEO；MODEL-INVENTORY；VLM-MODEL；HTTP-RECEIVER；PUSH-AUTHORIZATION</x:v>
+      </x:c>
+      <x:c r="V333" s="4" t="str">
+        <x:v>codex-ui-and-evidence</x:v>
+      </x:c>
+      <x:c r="W333" s="4"/>
+      <x:c r="X333" s="4"/>
+      <x:c r="Y333" s="4"/>
+      <x:c r="Z333" s="4"/>
+      <x:c r="AA333" s="4"/>
+      <x:c r="AB333" s="4"/>
+      <x:c r="AC333" s="4"/>
+    </x:row>
+    <x:row r="334" ht="285" customHeight="1">
+      <x:c r="A334" s="34" t="str">
+        <x:v>EVENT-013</x:v>
+      </x:c>
+      <x:c r="B334" s="34" t="str">
+        <x:v>J08</x:v>
+      </x:c>
+      <x:c r="C334" s="34" t="str">
+        <x:v>事件中心与统计</x:v>
+      </x:c>
+      <x:c r="D334" s="34" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E334" s="34" t="str">
+        <x:v>事件上报大模型审核：OpenAI接口放行与过滤</x:v>
+      </x:c>
+      <x:c r="F334" s="34" t="str">
+        <x:v>使用私有 FACE-VIDEO 绑定的视频。逐帧确认匹配与不匹配的人物目标，记录时间段、帧号/时间戳、目标框及人工判断。提示词如“穿红色衣服的人”；没有红衣正例时改用画面实际可辨认的衣着特征，不虚构正例。 复制基础行人检测/区域入侵场景到本轮隔离对象，上游使用普通检测节点，事件上报使用 BA_00004 的触发类事件；不得用独立 VLM 节点提前完成审核。固定ROI、告警间隔、去重、播放次数和时间窗。 OPENAI-VLM已由用户配置，测试按服务并发限制串行执行。</x:v>
+      </x:c>
+      <x:c r="G334" s="34" t="str">
+        <x:v>视频、审核模型与接口认证按资源ID绑定本轮私有配置。</x:v>
+      </x:c>
+      <x:c r="H334" s="34" t="str">
+        <x:v>1. 按私有配置核对OpenAI兼容服务的基地址、模型名、认证和chat/completions图像输入；模型使用实际served-model-name，保存脱敏响应证据。
+2. 关闭审核并重播固定正负片段，确认每个候选目标的基线上报，记录候选ID、片段、ROI及接收端时间窗。
+3. 在事件上报组件启用审核，选择OpenAI兼容接口，填写基地址、模型名、认证及人物特征提示词；保存刷新，认证回显和证据不得泄露密钥。
+4. 串行重播正例，核对设备向配置接口发送当前候选目标图，服务返回“是”，对应事件落库并成功HTTP上报。
+5. 串行重播负例，核对接口确实被调用且返回“否”，设备按审核过滤，事件中心及HTTP均无该候选普通告警；不能用请求失败冒充审核否定。
+6. 停启本轮任务后核对接口模式、模型与提示词仍有效，再关闭审核复测基线上报，最后清理本轮配置。</x:v>
+      </x:c>
+      <x:c r="I334" s="34" t="str">
+        <x:v>接口模式使用配置的服务与模型，真实图像请求有对应响应；“是”放行、“否”过滤，目标/帧/事件关联正确；配置停启后保持，关闭审核后恢复基线；认证仅以脱敏证据保存。</x:v>
+      </x:c>
+      <x:c r="J334" s="34" t="str">
+        <x:v>停止并删除本轮视频任务、临时通道与复制场景；恢复原推送、审核参数和视频播放配置。保留原有业务及历史事件，不修改共享模型服务。</x:v>
+      </x:c>
+      <x:c r="K334" s="34" t="str">
+        <x:v>视频哈希、标注片段与目标ROI、场景/任务/组件ID、审核模式、提示词与模型版本、审核调用及是/否结果、过滤记录、事件ID/抓拍/HTTP接收对账、修改前后配置与清理核对；认证信息脱敏。</x:v>
+      </x:c>
+      <x:c r="L334" s="34" t="str">
+        <x:v>UI主操作＋日志/接口只读交叉验证</x:v>
+      </x:c>
+      <x:c r="M334" s="34" t="str">
+        <x:v>受影响模块回归</x:v>
+      </x:c>
+      <x:c r="N334" s="34" t="str">
+        <x:v>OpenAI兼容多模态接口审核；不要求设备本地VLM可加载，不替代本地模式验收。不得重启或修改共享vLLM服务。</x:v>
+      </x:c>
+      <x:c r="O334" s="34" t="str">
+        <x:v>src/flow/alarm/TaskAlarmLlmReview.cc；src/flow/alarm/TaskAlarmEventBuilder.cc；data/resource/aiboxresource_bm1688/layout/actions.json</x:v>
+      </x:c>
+      <x:c r="P334" s="34" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="Q334" s="32" t="str">
+        <x:v>按逐目标可见事实核对功能；不以一次问答或总告警数减少替代审核链路验收。</x:v>
+      </x:c>
+      <x:c r="R334" s="34"/>
+      <x:c r="S334" s="34"/>
+      <x:c r="T334" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U334" s="4" t="str">
+        <x:v>DUT；FACE-VIDEO；MODEL-INVENTORY；OPENAI-VLM；HTTP-RECEIVER；PUSH-AUTHORIZATION</x:v>
+      </x:c>
+      <x:c r="V334" s="4" t="str">
+        <x:v>codex-ui-and-evidence</x:v>
+      </x:c>
+      <x:c r="W334" s="4"/>
+      <x:c r="X334" s="4"/>
+      <x:c r="Y334" s="4"/>
+      <x:c r="Z334" s="4"/>
+      <x:c r="AA334" s="4"/>
+      <x:c r="AB334" s="4"/>
+      <x:c r="AC334" s="4"/>
+    </x:row>
+    <x:row r="335" ht="285" customHeight="1">
+      <x:c r="A335" s="34" t="str">
+        <x:v>EVENT-014</x:v>
+      </x:c>
+      <x:c r="B335" s="34" t="str">
+        <x:v>J08</x:v>
+      </x:c>
+      <x:c r="C335" s="34" t="str">
+        <x:v>事件中心与统计</x:v>
+      </x:c>
+      <x:c r="D335" s="34" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E335" s="34" t="str">
+        <x:v>事件上报审核：提示词生效、事件类型与接口异常恢复</x:v>
+      </x:c>
+      <x:c r="F335" s="34" t="str">
+        <x:v>使用私有 FACE-VIDEO 绑定的视频。逐帧确认匹配与不匹配的人物目标，记录时间段、帧号/时间戳、目标框及人工判断。提示词如“穿红色衣服的人”；没有红衣正例时改用画面实际可辨认的衣着特征，不虚构正例。 复制基础行人检测/区域入侵场景到本轮隔离对象，上游使用普通检测节点，事件上报使用 BA_00004 的触发类事件；不得用独立 VLM 节点提前完成审核。固定ROI、告警间隔、去重、播放次数和时间窗。 已完成接口模式基础闭环，准备本轮可恢复参数变更。</x:v>
+      </x:c>
+      <x:c r="G335" s="34" t="str">
+        <x:v>视频、审核模型与接口认证按资源ID绑定本轮私有配置。</x:v>
+      </x:c>
+      <x:c r="H335" s="34" t="str">
+        <x:v>1. 冻结同一目标ROI，先使用匹配的衣着提示词，再改成该目标明显不具备的特征；逐次保存刷新、重播，核对实际请求使用新词且判断随语义变化。
+2. 在隔离场景分别验证触发类与定时类上报：保持审核开启，核对触发类走审核，定时类按原规则上报且不被该触发审核误过滤。
+3. 仅在本轮任务中暂填无效API Key，触发图像审核并记录401/认证失败；再暂改为确认未监听的本机回环端口以形成连接失败或配置超时，不停止共享服务。
+4. 按当前普通OpenAI审核分支核对故障降级：初始化/请求失败记录明确错误并允许原告警，不能标记为模型“是/否”；已有其他任务继续工作。
+5. 恢复正确认证、地址及提示词，保存回读并重播同一正负片段，确认真实审核调用和放行/过滤恢复，无需重启设备。
+6. 恢复原参数和事件类型，清理临时场景及任务，保留故障、降级、恢复三段证据。</x:v>
+      </x:c>
+      <x:c r="I335" s="34" t="str">
+        <x:v>提示词修改后实际使用新配置；仅触发类受审核控制。接口故障与模型否定分开记录，按当前普通OpenAI路径降级放行并有错误证据；恢复配置后重新审核成功。若产品降级策略变更，先按评审后的契约更新本预期。</x:v>
+      </x:c>
+      <x:c r="J335" s="34" t="str">
+        <x:v>停止并删除本轮视频任务、临时通道与复制场景；恢复原推送、审核参数和视频播放配置。保留原有业务及历史事件，不修改共享模型服务。</x:v>
+      </x:c>
+      <x:c r="K335" s="34" t="str">
+        <x:v>视频哈希、标注片段与目标ROI、场景/任务/组件ID、审核模式、提示词与模型版本、审核调用及是/否结果、过滤记录、事件ID/抓拍/HTTP接收对账、修改前后配置与清理核对；认证信息脱敏。</x:v>
+      </x:c>
+      <x:c r="L335" s="34" t="str">
+        <x:v>UI主操作＋日志/接口只读交叉验证</x:v>
+      </x:c>
+      <x:c r="M335" s="34" t="str">
+        <x:v>受影响模块回归</x:v>
+      </x:c>
+      <x:c r="N335" s="34" t="str">
+        <x:v>普通local_model/openai_vlm链路，不覆盖laya_v独立审核策略。网络故障仅改本轮任务配置，不更改服务或系统网络。</x:v>
+      </x:c>
+      <x:c r="O335" s="34" t="str">
+        <x:v>src/flow/alarm/TaskAlarmLlmReview.cc；src/flow/alarm/TaskAlarmEventBuilder.cc；data/resource/aiboxresource_bm1688/layout/actions.json</x:v>
+      </x:c>
+      <x:c r="P335" s="34" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="Q335" s="32" t="str">
+        <x:v>按逐目标可见事实核对功能；不以一次问答或总告警数减少替代审核链路验收。</x:v>
+      </x:c>
+      <x:c r="R335" s="34"/>
+      <x:c r="S335" s="34"/>
+      <x:c r="T335" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U335" s="4" t="str">
+        <x:v>DUT；FACE-VIDEO；MODEL-INVENTORY；OPENAI-VLM；HTTP-RECEIVER；PUSH-AUTHORIZATION</x:v>
+      </x:c>
+      <x:c r="V335" s="4" t="str">
+        <x:v>codex-ui-and-evidence</x:v>
+      </x:c>
+      <x:c r="W335" s="4"/>
+      <x:c r="X335" s="4"/>
+      <x:c r="Y335" s="4"/>
+      <x:c r="Z335" s="4"/>
+      <x:c r="AA335" s="4"/>
+      <x:c r="AB335" s="4"/>
+      <x:c r="AC335" s="4"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="P5:P312">
@@ -30600,7 +30907,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b25e11e15d0450b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e46bd8bf04b4aae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31802,7 +32109,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2804042a23b4547"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f6b0393802e43bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32405,7 +32712,7 @@
         <x:v>hardware</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>接在被测设备上的受支持USB摄像头；若产品/目标无此功能，确认不适用依据。</x:v>
+        <x:v>必测硬件：将受支持USB摄像头接在被测设备上，核对枚举、设备标识与实时画面。资源就绪状态记入私有配置，不沿用旧缺口跳过。</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
         <x:v>用户/设备管理员</x:v>
@@ -32489,10 +32796,54 @@
       <x:c r="F37" s="4" t="str"/>
       <x:c r="G37" s="4" t="str"/>
     </x:row>
+    <x:row r="38" ht="70.5" customHeight="1">
+      <x:c r="A38" s="4" t="str">
+        <x:v>OPENAI-VLM</x:v>
+      </x:c>
+      <x:c r="B38" s="4" t="str">
+        <x:v>OpenAI兼容多模态审核服务</x:v>
+      </x:c>
+      <x:c r="C38" s="4" t="str">
+        <x:v>network</x:v>
+      </x:c>
+      <x:c r="D38" s="4" t="str">
+        <x:v>可用的多模态chat/completions服务；核对/v1基地址、实际served-model-name、认证及图像输入。地址、API Key、并发限制只放私有配置。</x:v>
+      </x:c>
+      <x:c r="E38" s="4" t="str">
+        <x:v>用户/服务维护者</x:v>
+      </x:c>
+      <x:c r="F38" s="4" t="str">
+        <x:v>baseUrl；model；apiKey</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>为事件上报审核的接口模式单独预检；不以普通文本或TCP连通代替图像请求通过。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="70.5" customHeight="1">
+      <x:c r="A39" s="4" t="str">
+        <x:v>VLM-MODEL</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="str">
+        <x:v>视觉语言大模型运行资源</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="str">
+        <x:v>hardware</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>目标芯片可运行的 VLM 模型包、分词器及设备加载结果；原始 bmodel 不等于可导入模型。</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
+        <x:v>测试执行者/模型提供方</x:v>
+      </x:c>
+      <x:c r="F39" s="4"/>
+      <x:c r="G39" s="12" t="str">
+        <x:v>仅本地模型审核依赖此项；OpenAI接口模式独立检查OPENAI-VLM。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d23e039884142df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda230adafca946b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32642,7 +32993,7 @@
         <x:v>EVENT</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011</x:v>
+        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011、EVENT-012、EVENT-013、EVENT-014</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
         <x:v>按目标runMode及能力</x:v>
@@ -32682,7 +33033,7 @@
         <x:v>EVENT</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011</x:v>
+        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011、EVENT-012、EVENT-013、EVENT-014</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>按目标runMode及能力</x:v>
@@ -32702,7 +33053,7 @@
         <x:v>EVENT</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011</x:v>
+        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011、EVENT-012、EVENT-013、EVENT-014</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
         <x:v>按目标runMode及能力</x:v>
@@ -33442,7 +33793,7 @@
         <x:v>EVENT</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011</x:v>
+        <x:v>EVENT-001、EVENT-002、EVENT-003、EVENT-004、EVENT-005、EVENT-006、EVENT-007、EVENT-008、EVENT-009、EVENT-010、EVENT-011、EVENT-012、EVENT-013、EVENT-014</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
         <x:v>模块全部适用操作及异常路径</x:v>
@@ -33666,7 +34017,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5076af428b0d4fb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eff3e8fc86c4d50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34920,7 +35271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcdda22079d940b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b78bb90e58b4def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35262,13 +35613,13 @@
         <x:v>bm1688,cv186x,x86</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>FLOW-007</x:v>
+        <x:v>FLOW-007；EVENT-012；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
         <x:v>事件上报</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
-        <x:v>合法链运行；输入缺失/非法参数；保存回读；结果对应业务语义</x:v>
+        <x:v>合法链运行、非法参数及保存回读；审核关闭基线、本地/接口模式正例放行与反例过滤、目标ROI隔离、提示词修改、触发类边界和接口故障恢复。</x:v>
       </x:c>
       <x:c r="H14" s="9" t="str">
         <x:v>data/resource/aiboxresource_bm1688/layout/actions.json</x:v>
@@ -36540,7 +36891,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2c6fac99d5f4a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8623bb0eb2a24058"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52976,7 +53327,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M385" s="4" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-012；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N385" s="4" t="str">
         <x:v>未执行</x:v>
@@ -53021,7 +53372,7 @@
         <x:v>依次选每个枚举；非法值；保存刷新；触发依赖字段</x:v>
       </x:c>
       <x:c r="M386" s="9" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N386" s="9" t="str">
         <x:v>未执行</x:v>
@@ -53066,7 +53417,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M387" s="4" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N387" s="4" t="str">
         <x:v>未执行</x:v>
@@ -53109,7 +53460,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M388" s="9" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N388" s="9" t="str">
         <x:v>未执行</x:v>
@@ -53154,7 +53505,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M389" s="4" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N389" s="4" t="str">
         <x:v>未执行</x:v>
@@ -53199,7 +53550,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M390" s="9" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N390" s="9" t="str">
         <x:v>未执行</x:v>
@@ -53244,7 +53595,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M391" s="4" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N391" s="4" t="str">
         <x:v>未执行</x:v>
@@ -53289,7 +53640,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M392" s="9" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N392" s="9" t="str">
         <x:v>未执行</x:v>
@@ -53332,7 +53683,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M393" s="4" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-012</x:v>
       </x:c>
       <x:c r="N393" s="4" t="str">
         <x:v>未执行</x:v>
@@ -53375,7 +53726,7 @@
         <x:v>默认/合法替代/空/非法类型；按已确认范围测min、max及相邻越界；保存回读并验证行为</x:v>
       </x:c>
       <x:c r="M394" s="9" t="str">
-        <x:v>FLOW-009</x:v>
+        <x:v>FLOW-009；EVENT-012；EVENT-013；EVENT-014</x:v>
       </x:c>
       <x:c r="N394" s="9" t="str">
         <x:v>未执行</x:v>
@@ -61605,7 +61956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R881ad03912b04610"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f58264d00d4963"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/test/customer-journey/CosmoEdge-客户旅程测试用例.xlsx
+++ b/test/customer-journey/CosmoEdge-客户旅程测试用例.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="Reb80d4cc579641e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户旅程" sheetId="2" r:id="R45ea7e73c0684748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细用例" sheetId="3" r:id="R96ee922028ea4219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备矩阵" sheetId="4" r:id="Rbd69ea9a343c4395"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源与缺口" sheetId="5" r:id="R38f691ad12284363"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能覆盖" sheetId="6" r:id="R8a6446da02994f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算法覆盖" sheetId="7" r:id="R4c90900f26dc42f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件覆盖" sheetId="8" r:id="R037a9d8a1d9f4374"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数覆盖" sheetId="9" r:id="R849b99609d114bec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口覆盖" sheetId="10" r:id="R40f361b611ef46ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充检查" sheetId="11" r:id="R1065fad83c224c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R23b99d354dd94757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户旅程" sheetId="2" r:id="R0489923804994282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细用例" sheetId="3" r:id="R7f04b68864ca482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备矩阵" sheetId="4" r:id="R0a32b96f0f8a40da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源与缺口" sheetId="5" r:id="R9530c7664c8a4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能覆盖" sheetId="6" r:id="Rbb2f0b68d60d41dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算法覆盖" sheetId="7" r:id="R1ad84657c5404fde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件覆盖" sheetId="8" r:id="R1a5110ea10164377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数覆盖" sheetId="9" r:id="R796c798ff4da457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口覆盖" sheetId="10" r:id="R23a0a38321084537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充检查" sheetId="11" r:id="R5035c7d7798b4548"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="38">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -191,6 +191,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -365,7 +371,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="ExtraChecks" displayName="ExtraChecks" ref="A4:C5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="ExtraChecks" displayName="ExtraChecks" ref="A4:C8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="用例ID"/>
     <x:tableColumn id="2" name="检查ID"/>
@@ -376,8 +382,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TestCases" displayName="TestCases" ref="A4:AC335" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:AC335"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TestCases" displayName="TestCases" ref="A4:AC336" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:AC336"/>
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="用例ID"/>
     <x:tableColumn id="2" name="旅程"/>
@@ -463,8 +469,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="AlgorithmCoverage" displayName="AlgorithmCoverage" ref="A4:I48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:I48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="AlgorithmCoverage" displayName="AlgorithmCoverage" ref="A4:I49" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:I49"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="模板ID"/>
     <x:tableColumn id="2" name="模板名称"/>
@@ -762,7 +768,7 @@
         <x:v>用例总数</x:v>
       </x:c>
       <x:c r="B5" s="10" t="n">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -770,7 +776,7 @@
         <x:v>已通过</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P335,"通过")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P336,"通过")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -779,7 +785,7 @@
         <x:v>失败</x:v>
       </x:c>
       <x:c r="B7" s="10" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P335,"失败")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P336,"失败")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -788,7 +794,7 @@
         <x:v>阻塞</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P335,"阻塞")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P336,"阻塞")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -797,7 +803,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -805,7 +811,7 @@
         <x:v>部分完成</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P335,"部分完成")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P336,"部分完成")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -814,7 +820,7 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:f>COUNTIFS('详细用例'!P5:P335,"不适用")</x:f>
+        <x:f>COUNTIFS('详细用例'!P5:P336,"不适用")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -823,7 +829,7 @@
         <x:v>设计范围</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>12条旅程 / 28模块 / 44模板</x:v>
+        <x:v>12条旅程 / 28模块 / 45模板</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -863,7 +869,7 @@
         <x:v>文档性质</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>由v0.1评审稿持续维护的可执行主库；331条用例，不代表已经实测通过。</x:v>
+        <x:v>由v0.1评审稿持续维护的可执行主库；332条用例，不代表已经实测通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
@@ -991,7 +997,7 @@
         <x:v>用例库版本</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>1.6.0</x:v>
+        <x:v>1.7.0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
@@ -6594,7 +6600,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfae229dff67a4545"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc077c0cacfa24bb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6636,10 +6642,43 @@
       <x:c r="B5" s="26" t="str"/>
       <x:c r="C5" s="26" t="str"/>
     </x:row>
+    <x:row r="6" ht="48" customHeight="1">
+      <x:c r="A6" s="37" t="str">
+        <x:v>ALG-38874</x:v>
+      </x:c>
+      <x:c r="B6" s="37" t="str">
+        <x:v>OBB-METADATA</x:v>
+      </x:c>
+      <x:c r="C6" s="37" t="str">
+        <x:v>默认和各配置版本，以及节点参数声明，不含region、regionType、scheduleSupport、enableShieldedRegion、maxAreaCount、defaultFullScreen或confidenceConfig；直接confidence保留，保存重开不回流。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="37" t="str">
+        <x:v>ALG-38874</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="str">
+        <x:v>OBB-THRESHOLD</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>同一图片同一模型的稳定目标在直接阈值两侧有可对账的保留/过滤结果；无可用边界样本时记录具体缺口，不能以空结果或请求成功替代。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="37" t="str">
+        <x:v>ALG-38874</x:v>
+      </x:c>
+      <x:c r="B8" s="37" t="str">
+        <x:v>OBB-PERSISTENCE</x:v>
+      </x:c>
+      <x:c r="C8" s="37" t="str">
+        <x:v>临时阈值不改默认；显式保存的默认值重开可回读并影响后续分析；恢复后其他场景配置与结果保持基线。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08446b71f5a54c84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R052dead9eb954231"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6837,7 +6876,7 @@
         <x:v>单图批量与双图结果明确可解释</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>IMAGE → ALG-92* / ALG-93*</x:v>
+        <x:v>IMAGE → ALG-92* / ALG-93* / ALG-38874</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
         <x:v>选图片场景 → 上传单/多图 → 改本次参数 → 看命中证据及调试 → 上传A/B双图 → 设清空阈值 → 修正错误侧</x:v>
@@ -6964,7 +7003,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ff68db9cc054274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbe617a76afe4925"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17468,7 +17507,7 @@
       <x:c r="AB149" s="4" t="str"/>
       <x:c r="AC149" s="4" t="str"/>
     </x:row>
-    <x:row r="150" ht="38" customHeight="1">
+    <x:row r="150" ht="80" customHeight="1">
       <x:c r="A150" s="17" t="str">
         <x:v>IMAGE-007</x:v>
       </x:c>
@@ -17491,11 +17530,13 @@
         <x:v>IMAGE-MEDIA；FACE-ZIP匿名副本；UNIFORM-IMAGE；场景正负样本</x:v>
       </x:c>
       <x:c r="H150" s="17" t="str">
-        <x:v>1. 打开图片场景参数和编排
-2. 尝试套用视频区域跟踪计时节点</x:v>
+        <x:v>1. 打开图片场景参数、编排及图片分析参数面板，确认无视频检测区域、屏蔽区域和布防配置。
+2. 检查场景及节点参数声明，确认不暴露图片链路不支持的置信度偏移。
+3. 保存并重新打开场景，只读回查默认及各配置版本，确认旧字段没有回流。
+4. 尝试套用视频区域、跟踪和计时节点，核对无效语义提示；对照既有视频场景。</x:v>
       </x:c>
       <x:c r="I150" s="17" t="str">
-        <x:v>不出现或不接受无效的视频时序语义；裁剪使用检测框；旧视频场景保持原样。</x:v>
+        <x:v>图片场景不出现或不接受视频区域/时序语义及无效置信度偏移；保存重开后声明一致，直接置信度阈值保留。裁剪使用检测框；旧视频场景保持原样。OBB专项运行及阈值对照由ALG-38874覆盖。</x:v>
       </x:c>
       <x:c r="J150" s="17" t="str">
         <x:v>清理本轮上传与临时图片任务；恢复场景选择</x:v>
@@ -17522,7 +17563,7 @@
       <x:c r="R150" s="17" t="str"/>
       <x:c r="S150" s="17" t="str"/>
       <x:c r="T150" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U150" s="17" t="str">
         <x:v>DUT；IMAGE-MEDIA；MODEL-INVENTORY</x:v>
@@ -30891,6 +30932,83 @@
       <x:c r="AA335" s="4"/>
       <x:c r="AB335" s="4"/>
       <x:c r="AC335" s="4"/>
+    </x:row>
+    <x:row r="336" ht="180" customHeight="1">
+      <x:c r="A336" s="9" t="str">
+        <x:v>ALG-38874</x:v>
+      </x:c>
+      <x:c r="B336" s="9" t="str">
+        <x:v>J04/J07</x:v>
+      </x:c>
+      <x:c r="C336" s="9" t="str">
+        <x:v>逐算法业务验收</x:v>
+      </x:c>
+      <x:c r="D336" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E336" s="9" t="str">
+        <x:v>旋转框检测（OBB）模板与阈值生效</x:v>
+      </x:c>
+      <x:c r="F336" s="9" t="str">
+        <x:v>目标为bm1688/cv186x/x86且已安装匹配OBB模型；样本类别须与模型一致，包含可稳定检出且分值介于0和1的目标。缺模型或样本只阻塞本例，不以空结果判通过。</x:v>
+      </x:c>
+      <x:c r="G336" s="9" t="str">
+        <x:v>MODEL-INVENTORY核对模型类别；IMAGE-MEDIA与SCENARIO-TRUTH提供旋转目标正负/困难样本。素材路径仅在私有配置登记。</x:v>
+      </x:c>
+      <x:c r="H336" s="9" t="str">
+        <x:v>1. 核对目标芯片、OBB模型及类别；准备类别匹配的旋转目标图、负例与困难例，记录模型和样本哈希。
+2. 从旋转框检测模板创建本轮图片场景；检查参数和编排，保存后重新打开，并只读回查默认及各配置版本。
+3. 上传正例执行图片分析，核对原图、类别、分值与旋转框坐标/角度及叠加图；分别执行负例和困难例。
+4. 选择基准分值介于0和1的稳定目标，在其分值两侧设置直接置信度阈值并重放同一图片；记录低阈值保留、高阈值过滤的目标证据。
+5. 刷新或重新选择场景，确认临时阈值没有覆盖默认值；修改场景默认阈值、保存并重开，核对回读及新分析结果。
+6. 保存前后核对场景级及检测节点参数声明：不含置信度偏移；不提供视频区域、屏蔽区域或布防设置，直接置信度阈值仍可配置。
+7. 完成后释放本轮图片任务，删除临时场景并恢复修改的配置；核对其他视频场景保持原样。</x:v>
+      </x:c>
+      <x:c r="I336" s="9" t="str">
+        <x:v>场景保存/重开后旧字段不回流；直接置信度有效，临时覆盖与持久默认相互独立。正例返回与原图一致的旋转框、类别和分值，不能只以请求成功判通过；同一稳定目标在阈值两侧分别保留/过滤。负例、困难例按真值独立记录，不据少量样本宣称精度。</x:v>
+      </x:c>
+      <x:c r="J336" s="9" t="str">
+        <x:v>释放本轮图片任务并删除临时场景；恢复本轮改动的默认值；保留失败样本编号和证据，不影响既有业务。</x:v>
+      </x:c>
+      <x:c r="K336" s="9" t="str">
+        <x:v>模板及场景参数截图；各配置版本只读回查；模型/样本哈希；旋转框原始结果与叠加图；阈值对照；默认回读；清理记录。</x:v>
+      </x:c>
+      <x:c r="L336" s="9" t="str">
+        <x:v>UI创建配置与图片分析＋API只读核对</x:v>
+      </x:c>
+      <x:c r="M336" s="9" t="str">
+        <x:v>发布全量/OBB或图片参数变更</x:v>
+      </x:c>
+      <x:c r="N336" s="9" t="str">
+        <x:v>仅bm1688、cv186x、x86的OBB能力；每个平台独立取证。其他平台按能力证据记不适用；模板存在不等于模型已安装。</x:v>
+      </x:c>
+      <x:c r="O336" s="9" t="str">
+        <x:v>data/resource/aiboxresource_bm1688/algorithm_template/38874_yolo26_obb_20260914170000.json</x:v>
+      </x:c>
+      <x:c r="P336" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="Q336" s="12" t="str">
+        <x:v>新增OBB回归；未实机执行，不继承其他图片场景通过结果。</x:v>
+      </x:c>
+      <x:c r="R336" s="9"/>
+      <x:c r="S336" s="9"/>
+      <x:c r="T336" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U336" s="9" t="str">
+        <x:v>DUT;MODEL-INVENTORY;IMAGE-MEDIA;SCENARIO-TRUTH</x:v>
+      </x:c>
+      <x:c r="V336" s="9" t="str">
+        <x:v>codex-ui-and-evidence</x:v>
+      </x:c>
+      <x:c r="W336" s="9"/>
+      <x:c r="X336" s="9"/>
+      <x:c r="Y336" s="9"/>
+      <x:c r="Z336" s="9"/>
+      <x:c r="AA336" s="9"/>
+      <x:c r="AB336" s="9"/>
+      <x:c r="AC336" s="9"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="P5:P312">
@@ -30907,7 +31025,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e46bd8bf04b4aae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree55aceb121e4fc6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32109,7 +32227,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f6b0393802e43bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68fa384317ba42ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32843,7 +32961,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda230adafca946b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13d7efee2bc24684"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33733,7 +33851,7 @@
         <x:v>IMAGE</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>IMAGE-001、IMAGE-002、IMAGE-003、IMAGE-004、IMAGE-005、IMAGE-006、IMAGE-007、IMAGE-008、IMAGE-009、IMAGE-010、IMAGE-011、IMAGE-012、IMAGE-013</x:v>
+        <x:v>IMAGE-001、IMAGE-002、IMAGE-003、IMAGE-004、IMAGE-005、IMAGE-006、IMAGE-007、IMAGE-008、IMAGE-009、IMAGE-010、IMAGE-011、IMAGE-012、IMAGE-013、ALG-38874</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>模块全部适用操作及异常路径</x:v>
@@ -34017,7 +34135,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eff3e8fc86c4d50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfb436da5b54433b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35259,6 +35377,35 @@
       </x:c>
       <x:c r="I48" s="12" t="str"/>
     </x:row>
+    <x:row r="49" ht="65" customHeight="1">
+      <x:c r="A49" s="9" t="str">
+        <x:v>38874</x:v>
+      </x:c>
+      <x:c r="B49" s="9" t="str">
+        <x:v>旋转框检测算法</x:v>
+      </x:c>
+      <x:c r="C49" s="9" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="D49" s="9" t="str">
+        <x:v>bm1688,cv186x,x86</x:v>
+      </x:c>
+      <x:c r="E49" s="9" t="str">
+        <x:v>ALG-38874</x:v>
+      </x:c>
+      <x:c r="F49" s="9" t="str">
+        <x:v>匹配OBB模型类别的旋转目标正负/困难样本；稳定分值目标供阈值两侧对照</x:v>
+      </x:c>
+      <x:c r="G49" s="9" t="str">
+        <x:v>data/resource/aiboxresource_bm1688/algorithm_template/38874_yolo26_obb_20260914170000.json</x:v>
+      </x:c>
+      <x:c r="H49" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="I49" s="12" t="str">
+        <x:v>旧区域/置信度偏移字段清理回归；各平台独立验证</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="H5:H48">
     <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="失败"/>
@@ -35271,7 +35418,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b78bb90e58b4def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc7e1de4d664666"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36891,7 +37038,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8623bb0eb2a24058"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9194ff7277614f26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -61956,7 +62103,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f58264d00d4963"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd15cb3065b436f"/>
   </x:tableParts>
 </x:worksheet>
 </file>